--- a/artfynd/A 18589-2022 artfynd.xlsx
+++ b/artfynd/A 18589-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18589-2022 artfynd.xlsx
+++ b/artfynd/A 18589-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76232613</v>
+        <v>76232523</v>
       </c>
       <c r="B2" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1855</v>
+        <v>981</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Vit sminkrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Buglossoides arvensis var. arvensis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Simris: 400 m SV kyrkogården, Sk</t>
+          <t>Simris: NO Klingsrör, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446855.780204583</v>
+        <v>446856</v>
       </c>
       <c r="R2" t="n">
-        <v>6163753.903506353</v>
+        <v>6163754</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +739,9 @@
           <t>2016-06-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76232523</v>
+        <v>76232613</v>
       </c>
       <c r="B3" t="n">
-        <v>103493</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,30 +779,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>981</v>
+        <v>1855</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vit sminkrot</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buglossoides arvensis var. arvensis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Anthemis arvensis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Simris: NO Klingsrör, Sk</t>
+          <t>Simris: 400 m SV kyrkogården, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446855.780204583</v>
+        <v>446856</v>
       </c>
       <c r="R3" t="n">
-        <v>6163753.903506353</v>
+        <v>6163754</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -856,19 +836,9 @@
           <t>2016-06-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,53 +865,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76232435</v>
+        <v>9048</v>
       </c>
       <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>100117</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simris: NO Klingsrör, Sk</t>
+          <t>70 m S Stockadammen (lokal Nr: 837). - 91-198, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446857.3945300319</v>
+        <v>446818</v>
       </c>
       <c r="R4" t="n">
-        <v>6163653.94175281</v>
+        <v>6163434</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,22 +939,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>"Antal" avser maximala antalet romklumpar funna vid något besök (av flera) i angivet datumintervall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,65 +964,79 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
+          <t>Jon Loman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
+          <t>Jon Loman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76232559</v>
+        <v>73486799</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>100117</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Simris: O kyrkan, Sk</t>
+          <t>Snapparp, Södra våtmarken, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446857.3945300319</v>
+        <v>446815</v>
       </c>
       <c r="R5" t="n">
-        <v>6163653.94175281</v>
+        <v>6163446</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,22 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,68 +1074,68 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
+          <t>Kristian Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Marika Stenberg, Per Nyström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av groddjur</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76232477</v>
+        <v>76232559</v>
       </c>
       <c r="B6" t="n">
-        <v>98537</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222886</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simris: NO Klingsrör, Sk</t>
+          <t>Simris: O kyrkan, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446857.3945300319</v>
+        <v>446857</v>
       </c>
       <c r="R6" t="n">
-        <v>6163653.94175281</v>
+        <v>6163654</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1192,19 +1165,9 @@
           <t>2016-06-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,6 +1191,200 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>76232477</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101346</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Simris: NO Klingsrör, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>446857</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6163654</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Simrishamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sankt Olof</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>76232435</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Simris: NO Klingsrör, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>446857</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6163654</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Simrishamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sankt Olof</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-06-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-06-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
